--- a/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_PANATHINAIKOS AKTOR ATHENS.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_PANATHINAIKOS AKTOR ATHENS.xlsx
@@ -565,13 +565,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6312</v>
+        <v>9.2415</v>
       </c>
       <c r="E2" t="n">
-        <v>3.102800000000001</v>
+        <v>5.3209</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5282</v>
+        <v>3.9206</v>
       </c>
       <c r="G2" t="n">
         <v>7.246</v>
@@ -610,13 +610,13 @@
         <v>10.2363</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.5056</v>
+        <v>0.1047</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.9507</v>
+        <v>0.2673</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.5549</v>
+        <v>-0.1626</v>
       </c>
       <c r="V2" t="n">
         <v>0.2984000000000001</v>
@@ -643,13 +643,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8764</v>
+        <v>5.3516</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0861</v>
+        <v>4.8584</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7902</v>
+        <v>0.4933000000000002</v>
       </c>
       <c r="G3" t="n">
         <v>1.5555</v>
@@ -688,13 +688,13 @@
         <v>5.4594</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.499</v>
+        <v>-1.0236</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3467</v>
+        <v>0.4256</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1523</v>
+        <v>-1.4491</v>
       </c>
       <c r="V3" t="n">
         <v>1.6351</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4544</v>
+        <v>3.1527</v>
       </c>
       <c r="E4" t="n">
-        <v>5.494499999999999</v>
+        <v>4.257199999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0402</v>
+        <v>-1.1047</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0441</v>
+        <v>-2.1541</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0457</v>
+        <v>-8.301600000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.001500000000000334</v>
+        <v>6.147699999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>6.7662</v>
+        <v>3.9365</v>
       </c>
       <c r="K4" t="n">
-        <v>5.053199999999999</v>
+        <v>-1.6013</v>
       </c>
       <c r="L4" t="n">
-        <v>1.713</v>
+        <v>5.5377</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.722</v>
+        <v>-6.0905</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.0076</v>
+        <v>-6.7006</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7146</v>
+        <v>0.61</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1373</v>
+        <v>3.4121</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.7769</v>
+        <v>-3.6397</v>
       </c>
       <c r="R4" t="n">
-        <v>5.9142</v>
+        <v>7.0516</v>
       </c>
       <c r="S4" t="n">
-        <v>3.9963</v>
+        <v>-3.0111</v>
       </c>
       <c r="T4" t="n">
-        <v>3.892</v>
+        <v>-0.9453</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1043999999999999</v>
+        <v>-2.0658</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7235</v>
+        <v>4.9055</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3867</v>
+        <v>4.9055</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9683000000000002</v>
+        <v>1.4539</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2945</v>
+        <v>7.7941</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.3261</v>
+        <v>-6.3401</v>
       </c>
       <c r="G5" t="n">
         <v>-4.0069</v>
@@ -844,13 +844,13 @@
         <v>10.0088</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0198</v>
+        <v>1.5056</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6215000000000001</v>
+        <v>0.8781</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6413</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>0.08840000000000048</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4900999999999998</v>
+        <v>0.3022999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3897</v>
+        <v>2.2976</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8997</v>
+        <v>-1.9954</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1528</v>
+        <v>1.0441</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5315000000000002</v>
+        <v>1.0457</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6841999999999999</v>
+        <v>-0.001500000000000334</v>
       </c>
       <c r="J6" t="n">
-        <v>2.321</v>
+        <v>6.7662</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8367</v>
+        <v>5.053199999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4844</v>
+        <v>1.713</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4738</v>
+        <v>-5.722</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3053</v>
+        <v>-4.0076</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1685</v>
+        <v>-1.7146</v>
       </c>
       <c r="P6" t="n">
         <v>1.1373</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2748</v>
+        <v>-4.7769</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4121</v>
+        <v>5.9142</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4791</v>
+        <v>-0.1556</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1851</v>
+        <v>0.6950999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2940999999999999</v>
+        <v>-0.8508000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.9737</v>
+        <v>-1.7235</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1583</v>
+        <v>-0.3867</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.132</v>
+        <v>-1.3367</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3775000000000001</v>
+        <v>0.007000000000000006</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2828999999999999</v>
+        <v>-1.1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6604</v>
+        <v>1.107</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4276</v>
@@ -1000,13 +1000,13 @@
         <v>0.6824</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3975000000000001</v>
+        <v>0.02700000000000002</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6347</v>
+        <v>-0.1824</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2372</v>
+        <v>0.2093</v>
       </c>
       <c r="V7" t="n">
         <v>1.0901</v>
@@ -1033,13 +1033,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2564</v>
+        <v>-0.06160000000000007</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4935</v>
+        <v>-0.8437000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7498999999999999</v>
+        <v>0.7822</v>
       </c>
       <c r="G8" t="n">
         <v>0.00379999999999997</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1341</v>
+        <v>-0.4519</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4191</v>
+        <v>0.06889999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5532</v>
+        <v>-0.5208</v>
       </c>
       <c r="V8" t="n">
         <v>0.3867</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>P. KALAITZAKIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,67 +1108,67 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09850000000000048</v>
+        <v>-0.4757</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7788</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6804</v>
+        <v>0.4663</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1541</v>
+        <v>-0.4996</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.301600000000001</v>
+        <v>-0.9665</v>
       </c>
       <c r="I9" t="n">
-        <v>6.147699999999999</v>
+        <v>0.4669</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9365</v>
+        <v>-0.7265</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6013</v>
+        <v>-0.7265</v>
       </c>
       <c r="L9" t="n">
-        <v>5.5377</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.0905</v>
+        <v>0.2269</v>
       </c>
       <c r="N9" t="n">
-        <v>-6.7006</v>
+        <v>-0.24</v>
       </c>
       <c r="O9" t="n">
-        <v>0.61</v>
+        <v>0.4669</v>
       </c>
       <c r="P9" t="n">
-        <v>3.4121</v>
+        <v>0.6824</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.6397</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>7.0516</v>
+        <v>0.6824</v>
       </c>
       <c r="S9" t="n">
-        <v>-6.0652</v>
+        <v>-0.6585</v>
       </c>
       <c r="T9" t="n">
-        <v>-3.4235</v>
+        <v>-0.2155</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.6416</v>
+        <v>-0.443</v>
       </c>
       <c r="V9" t="n">
-        <v>4.9055</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>4.9055</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. KALAITZAKIS</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5403</v>
+        <v>-2.166</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9419999999999999</v>
+        <v>1.4769</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4017</v>
+        <v>-3.6431</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4996</v>
+        <v>-0.1528</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9665</v>
+        <v>0.5315000000000002</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4669</v>
+        <v>-0.6841999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7265</v>
+        <v>2.321</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7265</v>
+        <v>1.8367</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.4844</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2269</v>
+        <v>-2.4738</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.24</v>
+        <v>-1.3053</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4669</v>
+        <v>-1.1685</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6824</v>
+        <v>1.1373</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.2748</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6824</v>
+        <v>3.4121</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7231</v>
+        <v>0.8231999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2155</v>
+        <v>1.2724</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5077</v>
+        <v>-0.4492</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-3.9737</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-4.132</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. LESSORT</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7087</v>
+        <v>-2.2801</v>
       </c>
       <c r="E11" t="n">
-        <v>4.8517</v>
+        <v>-0.3603</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.5604</v>
+        <v>-1.9198</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03950000000000026</v>
+        <v>0.1009</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7361</v>
+        <v>1.7253</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6965</v>
+        <v>-1.6243</v>
       </c>
       <c r="J11" t="n">
-        <v>5.9986</v>
+        <v>0.4809</v>
       </c>
       <c r="K11" t="n">
-        <v>3.0928</v>
+        <v>2.3272</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9058</v>
+        <v>-1.8464</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.0382</v>
+        <v>-0.38</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.8291</v>
+        <v>-0.602</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2094</v>
+        <v>0.222</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0473</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q11" t="n">
-        <v>-12.056</v>
+        <v>-1.3648</v>
       </c>
       <c r="R11" t="n">
-        <v>10.0088</v>
+        <v>1.1374</v>
       </c>
       <c r="S11" t="n">
-        <v>7.463900000000001</v>
+        <v>-0.1317</v>
       </c>
       <c r="T11" t="n">
-        <v>7.8671</v>
+        <v>0.3653</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4033</v>
+        <v>-0.497</v>
       </c>
       <c r="V11" t="n">
-        <v>-7.0856</v>
+        <v>-2.0219</v>
       </c>
       <c r="W11" t="n">
-        <v>3.042</v>
+        <v>0.1583</v>
       </c>
       <c r="X11" t="n">
-        <v>-10.1276</v>
+        <v>-2.1802</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.361800000000001</v>
+        <v>-3.011</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4239</v>
+        <v>-3.1904</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06210000000000004</v>
+        <v>0.1793999999999998</v>
       </c>
       <c r="G12" t="n">
         <v>0.4937000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>1.1374</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1951</v>
+        <v>-0.8442000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2211</v>
+        <v>-0.9876</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02610000000000001</v>
+        <v>0.1434</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1583</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>N. HAYES-DAVIS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4079</v>
+        <v>-5.5393</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1326</v>
+        <v>-6.4573</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2753</v>
+        <v>0.9181</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1009</v>
+        <v>-16.2428</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7253</v>
+        <v>-8.3262</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6243</v>
+        <v>-7.9165</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4809</v>
+        <v>-7.2643</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3272</v>
+        <v>-0.1180000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.8464</v>
+        <v>-7.146200000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.38</v>
+        <v>-8.978399999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.602</v>
+        <v>-8.2082</v>
       </c>
       <c r="O13" t="n">
-        <v>0.222</v>
+        <v>-0.7704</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2275</v>
+        <v>5.4593</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.3648</v>
+        <v>-7.5067</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1374</v>
+        <v>12.966</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2595</v>
+        <v>0.4969999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.407</v>
+        <v>0.9111999999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8525</v>
+        <v>-0.4141</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.0219</v>
+        <v>4.7472</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1583</v>
+        <v>7.4024</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1802</v>
+        <v>-2.6553</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. HAYES-DAVIS</t>
+          <t>M. LESSORT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.746600000000001</v>
+        <v>-7.1222</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.001900000000001</v>
+        <v>-0.9583999999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7446999999999997</v>
+        <v>-6.1639</v>
       </c>
       <c r="G14" t="n">
-        <v>-16.2428</v>
+        <v>-0.03950000000000026</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.3262</v>
+        <v>-1.7361</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.9165</v>
+        <v>1.6965</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.2643</v>
+        <v>5.9986</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1180000000000001</v>
+        <v>3.0928</v>
       </c>
       <c r="L14" t="n">
-        <v>-7.146200000000001</v>
+        <v>2.9058</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.978399999999999</v>
+        <v>-6.0382</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.2082</v>
+        <v>-4.8291</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7704</v>
+        <v>-1.2094</v>
       </c>
       <c r="P14" t="n">
-        <v>5.4593</v>
+        <v>-2.0473</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.5067</v>
+        <v>-12.056</v>
       </c>
       <c r="R14" t="n">
-        <v>12.966</v>
+        <v>10.0088</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.7103</v>
+        <v>2.0503</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6334</v>
+        <v>2.0574</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.077</v>
+        <v>-0.006899999999999962</v>
       </c>
       <c r="V14" t="n">
-        <v>4.7472</v>
+        <v>-7.0856</v>
       </c>
       <c r="W14" t="n">
-        <v>7.4024</v>
+        <v>3.042</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.6553</v>
+        <v>-10.1276</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.0062</v>
+        <v>-9.5037</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.4399</v>
+        <v>-7.794</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.5664</v>
+        <v>-1.7096</v>
       </c>
       <c r="G15" t="n">
         <v>6.053699999999999</v>
@@ -1624,13 +1624,13 @@
         <v>12.0562</v>
       </c>
       <c r="S15" t="n">
-        <v>-7.4658</v>
+        <v>-1.9633</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.818099999999999</v>
+        <v>-0.1722999999999998</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.6477</v>
+        <v>-1.7909</v>
       </c>
       <c r="V15" t="n">
         <v>-3.1302</v>
@@ -1657,13 +1657,13 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>-15.6187</v>
+        <v>-10.6506</v>
       </c>
       <c r="E16" t="n">
-        <v>3.281399999999998</v>
+        <v>4.359</v>
       </c>
       <c r="F16" t="n">
-        <v>-18.9007</v>
+        <v>-15.0097</v>
       </c>
       <c r="G16" t="n">
         <v>-7.025599999999999</v>
@@ -1672,7 +1672,7 @@
         <v>-15.7518</v>
       </c>
       <c r="I16" t="n">
-        <v>8.726900000000001</v>
+        <v>8.726899999999995</v>
       </c>
       <c r="J16" t="n">
         <v>45.4067</v>
@@ -1690,7 +1690,7 @@
         <v>-43.236</v>
       </c>
       <c r="O16" t="n">
-        <v>-9.196499999999999</v>
+        <v>-9.1965</v>
       </c>
       <c r="P16" t="n">
         <v>4.549000000000003</v>
@@ -1702,13 +1702,13 @@
         <v>80.75300000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>-8.2011</v>
+        <v>-3.2321</v>
       </c>
       <c r="T16" t="n">
-        <v>3.360500000000002</v>
+        <v>4.4382</v>
       </c>
       <c r="U16" t="n">
-        <v>-11.5615</v>
+        <v>-7.670000000000002</v>
       </c>
       <c r="V16" t="n">
         <v>-4.9418</v>
